--- a/resources/templates/standard/F1101-02.xlsx
+++ b/resources/templates/standard/F1101-02.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>신임 교육 일지</t>
   </si>
@@ -726,11 +729,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -740,18 +745,18 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N1" s="4"/>
       <c r="O1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P1" s="4"/>
       <c r="Q1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R1" s="4"/>
     </row>
@@ -817,7 +822,7 @@
     </row>
     <row r="5" ht="21.95" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -828,7 +833,7 @@
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -841,7 +846,7 @@
     </row>
     <row r="6" ht="21.95" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -852,7 +857,7 @@
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
@@ -865,7 +870,7 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -1187,7 +1192,7 @@
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B23" s="21"/>
       <c r="C23" s="21"/>
@@ -1409,7 +1414,7 @@
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -1420,7 +1425,7 @@
       <c r="H34" s="9"/>
       <c r="I34" s="9"/>
       <c r="J34" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="11"/>
